--- a/public/Book1.xlsx
+++ b/public/Book1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\OneDrive\Escritorio\Proyectos\deposito-app\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8d8713509c400096/Escritorio/Proyectos/deposito-app/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64F7C82-7F32-4254-B72B-E6B36F8C4A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{B64F7C82-7F32-4254-B72B-E6B36F8C4A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BADBD3DF-AAD7-45AD-88C5-65676AAE56AE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5A30A731-61CF-4EA8-AC20-06E1F211FE61}"/>
   </bookViews>
@@ -36,31 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
-  <si>
-    <t>Taladro</t>
-  </si>
-  <si>
-    <t>Generador</t>
-  </si>
-  <si>
-    <t>Herramientas</t>
-  </si>
-  <si>
-    <t>Amoladora</t>
-  </si>
-  <si>
-    <t>Soldadora</t>
-  </si>
-  <si>
-    <t>Stihl</t>
-  </si>
-  <si>
-    <t>Lusqtoff</t>
-  </si>
-  <si>
-    <t>Black&amp;Decker</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>description</t>
   </si>
@@ -72,13 +48,43 @@
   </si>
   <si>
     <t>code</t>
+  </si>
+  <si>
+    <t>Herramienta 1</t>
+  </si>
+  <si>
+    <t>Herramienta 2</t>
+  </si>
+  <si>
+    <t>Herramienta 3</t>
+  </si>
+  <si>
+    <t>Herramienta 4</t>
+  </si>
+  <si>
+    <t>Herramienta 5</t>
+  </si>
+  <si>
+    <t>Marca 1</t>
+  </si>
+  <si>
+    <t>Marca 2</t>
+  </si>
+  <si>
+    <t>Marca 3</t>
+  </si>
+  <si>
+    <t>Marca 4</t>
+  </si>
+  <si>
+    <t>Marca 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +96,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -135,6 +147,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,89 +480,90 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
+        <v>11111</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2">
-        <v>1234567891789</v>
+        <v>1234567777888</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>111112</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2">
-        <v>1234567891456</v>
+        <v>1234569999888</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>111113</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2">
-        <v>1234567891963</v>
+        <v>1234561111888</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4</v>
+        <v>111114</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2">
-        <v>1234567891753</v>
+        <v>1234562222555</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>1111115</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2">
-        <v>1234567891741</v>
+        <v>1234569999444</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>